--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484630_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484630_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.760999999999999</v>
+        <v>7.8049</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4276</v>
+        <v>6.5211</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3334</v>
+        <v>1.2838</v>
       </c>
       <c r="G2" t="n">
         <v>5.4775</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6525</v>
+        <v>0.6965</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9578</v>
+        <v>1.0513</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3053</v>
+        <v>-0.3549</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9346</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3668</v>
+        <v>3.9661</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8815</v>
+        <v>2.4312</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4853</v>
+        <v>1.5349</v>
       </c>
       <c r="G3" t="n">
         <v>5.692</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.927</v>
+        <v>-1.3277</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9728</v>
+        <v>-0.4231</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9542</v>
+        <v>-0.9046</v>
       </c>
       <c r="V3" t="n">
         <v>2.5339</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8816</v>
+        <v>3.0648</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8937</v>
+        <v>2.0139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9879</v>
+        <v>1.0508</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3978</v>
+        <v>2.0906</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6899</v>
+        <v>0.9463</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2921</v>
+        <v>1.1443</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2451</v>
+        <v>2.0604</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9598</v>
+        <v>0.6594</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.7147</v>
+        <v>1.401</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8474</v>
+        <v>0.0302</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.27</v>
+        <v>0.2869</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5774</v>
+        <v>-0.2567</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7489</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>1.879</v>
+        <v>-0.2928</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7926</v>
+        <v>-0.1248</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0864</v>
+        <v>-0.168</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3115</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3115</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3555</v>
+        <v>1.8404</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4781</v>
+        <v>1.0011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8774</v>
+        <v>0.8393</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0906</v>
+        <v>0.3978</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9463</v>
+        <v>2.6899</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1443</v>
+        <v>-2.2921</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0604</v>
+        <v>2.2451</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6594</v>
+        <v>3.9598</v>
       </c>
       <c r="L5" t="n">
-        <v>1.401</v>
+        <v>-1.7147</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0302</v>
+        <v>-1.8474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2869</v>
+        <v>-1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2567</v>
+        <v>-0.5774</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.002</v>
+        <v>0.8379</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6606</v>
+        <v>0.9001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3414</v>
+        <v>-0.0622</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>-0.3115</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9109</v>
+        <v>-0.3115</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1264</v>
+        <v>1.7335</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2202</v>
+        <v>3.0007</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0938</v>
+        <v>-1.2672</v>
       </c>
       <c r="G6" t="n">
         <v>1.7467</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0905</v>
+        <v>-0.129</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.004</v>
+        <v>-0.1774</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6231</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1227</v>
+        <v>1.5079</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7292</v>
+        <v>1.9905</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.4826</v>
       </c>
       <c r="G7" t="n">
         <v>1.9587</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8518</v>
+        <v>-0.4666</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4955</v>
+        <v>-0.2342</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3563</v>
+        <v>-0.2325</v>
       </c>
       <c r="V7" t="n">
         <v>-1.267</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>0.0365</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9653</v>
+        <v>-1.0306</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9443</v>
+        <v>1.0671</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9433</v>
+        <v>0.0373</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6484</v>
+        <v>1.2138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2949</v>
+        <v>-1.1764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6735</v>
+        <v>-0.0174</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1796</v>
+        <v>1.223</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5062</v>
+        <v>-1.2404</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2698</v>
+        <v>0.0548</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5312</v>
+        <v>-0.0092</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8011</v>
+        <v>0.064</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1109</v>
+        <v>-0.412</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2919</v>
+        <v>-0.0969</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4028</v>
+        <v>-0.3151</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. BOU MINARRO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3331</v>
+        <v>-0.0516</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2444</v>
+        <v>0.5682</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0888</v>
+        <v>-0.6198</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3834</v>
+        <v>2.2805</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6719000000000001</v>
+        <v>2.8992</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2885</v>
+        <v>-0.6187</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6719000000000001</v>
+        <v>1.8749</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6719000000000001</v>
+        <v>3.0062</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.1313</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2885</v>
+        <v>0.4056</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1069</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2885</v>
+        <v>0.5125</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1833</v>
+        <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0165</v>
+        <v>0.1469</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5155</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>-0.3686</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.8455</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3645</v>
+        <v>-0.1329</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0324</v>
+        <v>1.0343</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3969</v>
+        <v>-1.1673</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2805</v>
+        <v>0.9433</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8992</v>
+        <v>0.6484</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6187</v>
+        <v>0.2949</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8749</v>
+        <v>0.6735</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0062</v>
+        <v>1.1796</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1313</v>
+        <v>-0.5062</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4056</v>
+        <v>0.2698</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1069</v>
+        <v>-0.5312</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5125</v>
+        <v>0.8011</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.166</v>
+        <v>-0.2649</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0203</v>
+        <v>0.3609</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1457</v>
+        <v>-0.6258</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.8455</v>
+        <v>-1.9109</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8559</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>I. BOU MINARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3814</v>
+        <v>-0.2122</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3741</v>
+        <v>-0.1482</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9927</v>
+        <v>-0.064</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0373</v>
+        <v>0.3834</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2138</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1764</v>
+        <v>-0.2885</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0174</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.223</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2404</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0548</v>
+        <v>-0.2885</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0092</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.064</v>
+        <v>-0.2885</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8298</v>
+        <v>0.1374</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4404</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3894</v>
+        <v>0.0413</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2471</v>
+        <v>-7.1473</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1985</v>
+        <v>-3.4703</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0486</v>
+        <v>-3.677</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5469</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7606000000000001</v>
+        <v>0.3392</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.276</v>
+        <v>0.4521</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4846</v>
+        <v>-0.113</v>
       </c>
       <c r="V12" t="n">
         <v>-5.3898</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.3089</v>
+        <v>12.4101</v>
       </c>
       <c r="E13" t="n">
-        <v>12.811</v>
+        <v>13.9119</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.502100000000001</v>
+        <v>-1.502</v>
       </c>
       <c r="G13" t="n">
         <v>19.4609</v>
@@ -1459,7 +1459,7 @@
         <v>1.2791</v>
       </c>
       <c r="P13" t="n">
-        <v>3.665099999999999</v>
+        <v>3.6651</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.7444</v>
@@ -1468,10 +1468,10 @@
         <v>17.4095</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0136</v>
+        <v>-0.9125000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2672</v>
+        <v>2.3681</v>
       </c>
       <c r="U13" t="n">
         <v>-3.2808</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8039</v>
+        <v>3.1491</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6211</v>
+        <v>3.1019</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1828</v>
+        <v>0.0472</v>
       </c>
       <c r="G14" t="n">
         <v>1.5809</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>0.077</v>
+        <v>0.4221</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1485</v>
+        <v>0.3322</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2255</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.3293</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.268</v>
+        <v>1.7837</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8351</v>
+        <v>2.1236</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5671</v>
+        <v>-0.3398</v>
       </c>
       <c r="G16" t="n">
         <v>-3.2783</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4869</v>
+        <v>1.0026</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4744</v>
+        <v>0.7628</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0125</v>
+        <v>0.2398</v>
       </c>
       <c r="V16" t="n">
         <v>6.0752</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1458</v>
+        <v>1.1429</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8522</v>
+        <v>0.9483</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2937</v>
+        <v>0.1946</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4519</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3736</v>
+        <v>0.3707</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0905</v>
+        <v>0.1867</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2831</v>
+        <v>0.184</v>
       </c>
       <c r="V17" t="n">
         <v>0.1246</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4426</v>
+        <v>0.0757</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0666</v>
+        <v>3.0439</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5092</v>
+        <v>-2.9682</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8688</v>
+        <v>-0.8653</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9647</v>
+        <v>-0.0544</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8336</v>
+        <v>-0.8109</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4339</v>
+        <v>1.9146</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4335</v>
+        <v>2.4367</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0004</v>
+        <v>-0.5221</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.7799</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3982</v>
+        <v>-2.4911</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.2888</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2828</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0603</v>
+        <v>0.1327</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3673</v>
+        <v>0.0668</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5339</v>
+        <v>2.2743</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.8113</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5339</v>
+        <v>-1.537</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.746</v>
+        <v>-0.1148</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7554</v>
+        <v>2.1627</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5015</v>
+        <v>-2.2775</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8653</v>
+        <v>1.8688</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0544</v>
+        <v>-0.9647</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8109</v>
+        <v>2.8336</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9146</v>
+        <v>2.4339</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4367</v>
+        <v>0.4335</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5221</v>
+        <v>2.0004</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7799</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.4911</v>
+        <v>-1.3982</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2888</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.7325</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2217</v>
+        <v>-0.2711</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4673</v>
+        <v>-0.4614</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2743</v>
+        <v>-2.5339</v>
       </c>
       <c r="W21" t="n">
-        <v>3.8113</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.537</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5587</v>
+        <v>-2.5515</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.207</v>
+        <v>-0.3513</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3518</v>
+        <v>-2.2001</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.5884</v>
+        <v>-3.2416</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.5879</v>
+        <v>-2.3187</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0005</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.8848</v>
+        <v>-0.4237</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0131</v>
+        <v>0.1143</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.8717</v>
+        <v>-0.538</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.7036</v>
+        <v>-2.818</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.5748</v>
+        <v>-2.433</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1288</v>
+        <v>-0.3849</v>
       </c>
       <c r="P22" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.6651</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.7489</v>
+        <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3216</v>
+        <v>0.7775</v>
       </c>
       <c r="T22" t="n">
-        <v>3.8432</v>
+        <v>0.6667</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5216</v>
+        <v>0.1108</v>
       </c>
       <c r="V22" t="n">
-        <v>3.6244</v>
+        <v>-0.8204</v>
       </c>
       <c r="W22" t="n">
-        <v>3.4998</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1246</v>
+        <v>-1.1424</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8429</v>
+        <v>-2.9686</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5436</v>
+        <v>-2.3507</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2992</v>
+        <v>-0.6178</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2416</v>
+        <v>-2.9034</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3187</v>
+        <v>-2.2684</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.635</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4237</v>
+        <v>-1.5521</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1143</v>
+        <v>-1.0778</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.538</v>
+        <v>-0.4743</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.818</v>
+        <v>-1.3513</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.433</v>
+        <v>-1.1907</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3849</v>
+        <v>-0.1606</v>
       </c>
       <c r="P23" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4861</v>
+        <v>0.0735</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4744</v>
+        <v>0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0118</v>
+        <v>-0.0441</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8204</v>
+        <v>-0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1424</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1778</v>
+        <v>-4.3332</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9277</v>
+        <v>-3.5147</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2502</v>
+        <v>-0.8185</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9034</v>
+        <v>-8.5884</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2684</v>
+        <v>-5.5879</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.635</v>
+        <v>-3.0005</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5521</v>
+        <v>-4.8848</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0778</v>
+        <v>-2.0131</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4743</v>
+        <v>-2.8717</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3513</v>
+        <v>-3.7036</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1907</v>
+        <v>-3.5748</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1606</v>
+        <v>-0.1288</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0995</v>
+        <v>2.7489</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1357</v>
+        <v>1.5471</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4593</v>
+        <v>1.5355</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6765</v>
+        <v>0.0117</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3219</v>
+        <v>3.6244</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.4998</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3219</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.609400000000001</v>
+        <v>-8.42</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8008</v>
+        <v>-6.5124</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8085</v>
+        <v>-1.9076</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4323</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1534</v>
+        <v>0.3428</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.405</v>
+        <v>-0.1165</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5584</v>
+        <v>0.4593</v>
       </c>
       <c r="V25" t="n">
         <v>0.0519</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.309</v>
+        <v>-9.385999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.502</v>
+        <v>1.502000000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.811</v>
+        <v>-10.8877</v>
       </c>
       <c r="G26" t="n">
         <v>-19.4608</v>
@@ -2455,13 +2455,13 @@
         <v>-1.923</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3853999999999993</v>
+        <v>0.3854000000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>1.664300000000001</v>
+        <v>1.6643</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.279</v>
+        <v>-1.279000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-19.8461</v>
@@ -2482,16 +2482,16 @@
         <v>13.7442</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0136</v>
+        <v>3.9365</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2807</v>
+        <v>3.2808</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2671</v>
+        <v>0.656</v>
       </c>
       <c r="V26" t="n">
-        <v>9.803500000000001</v>
+        <v>9.8035</v>
       </c>
       <c r="W26" t="n">
         <v>15.2452</v>
